--- a/public/data_template.xlsx
+++ b/public/data_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="입력순서" sheetId="1" r:id="rId1"/>
+    <sheet name="0_안내" sheetId="1" r:id="rId1"/>
     <sheet name="1_주최사" sheetId="2" r:id="rId2"/>
     <sheet name="2_행사" sheetId="3" r:id="rId3"/>
     <sheet name="3_행사개최" sheetId="4" r:id="rId4"/>
@@ -401,74 +401,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:B20"/>
   <cols>
-    <col min="1" max="1" width="65.83203125" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="70.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>FLIT 데이터 입력 가이드</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
+        <v>FLIT 데이터 입력 양식 사용 안내</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>입력 순서 (반드시 순서대로!)</v>
+        <v>📌 작성 순서</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. [1_주최사] 주최사 정보</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>1_주최사 시트 → 주최사 정보 입력 (* 필수)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. [2_행사] 행사(브랜드) 정보</v>
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2_행사 시트 → 행사 브랜드 정보 입력</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. [3_행사개최] 실제 개최 정보 (날짜/장소)</v>
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>3_행사개최 시트 → 행사 개최 회차별 정보 입력</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. [4_모집공고] 모집공고</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>4_모집공고 시트 → 모집공고 정보 입력</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>각 시트 2~3행은 예시입니다. 삭제 후 실제 데이터를 입력하세요.</v>
+        <v>📌 주의사항</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>행사명/주최사명은 시트 간에 정확히 일치해야 합니다!</v>
+        <v>·</v>
+      </c>
+      <c r="B10" t="str">
+        <v>* 표시된 컬럼은 필수 입력값입니다.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>·</v>
+      </c>
+      <c r="B11" t="str">
+        <v>3_행사개최의 행사명은 2_행사에 등록된 행사명과 동일해야 합니다.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>·</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3_행사개최의 주최사명은 1_주최사에 등록된 주최사명과 동일해야 합니다.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>·</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4_모집공고의 행사명은 3_행사개최에 등록된 행사명과 동일해야 합니다.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>·</v>
+      </c>
+      <c r="B14" t="str">
+        <v>날짜는 YYYY-MM-DD 형식으로 입력하세요. 예) 2026-04-10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>·</v>
+      </c>
+      <c r="B15" t="str">
+        <v>참가비는 숫자만 입력하세요 (원 단위). 무료인 경우 0 입력.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>·</v>
+      </c>
+      <c r="B16" t="str">
+        <v>카테고리 유효값: 플리마켓 / 푸드트럭 / 플리+푸드</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>·</v>
+      </c>
+      <c r="B17" t="str">
+        <v>상태 유효값: OPEN (모집중) / CLOSED (마감)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>📌 버전</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>v3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-31 — 현재 DB 스키마 기준</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C3"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -488,53 +563,37 @@
         <v>서울플리마켓협회</v>
       </c>
       <c r="B2" t="str">
-        <v>서울 지역 플리마켓 기획 운영 단체</v>
+        <v>서울 주요 플리마켓을 주최하는 협회입니다.</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>https://example.com/logo.png</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>한강문화재단</v>
+        <v>한강공원관리사업소</v>
       </c>
       <c r="B3" t="str">
-        <v>한강공원 문화행사 전문 기획사</v>
+        <v/>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>맛있는축제</v>
-      </c>
-      <c r="B4" t="str">
-        <v>전국 푸드트럭 페스티벌 전문</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>[안내] 주최사명은 필수입니다</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D4"/>
   <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
     <col min="4" max="4" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -560,7 +619,7 @@
         <v>플리마켓</v>
       </c>
       <c r="C2" t="str">
-        <v>서울 대표 야간 플리마켓</v>
+        <v>서울 대표 야시장 플리마켓</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -568,13 +627,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>여의도 한강 푸드트럭</v>
+        <v>뚝섬 플리마켓</v>
       </c>
       <c r="B3" t="str">
-        <v>푸드트럭페스티벌</v>
+        <v>플리+푸드</v>
       </c>
       <c r="C3" t="str">
-        <v>한강공원 푸드트럭 행사</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -582,59 +641,35 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>성수 팝업마켓</v>
+        <v>한강 푸드트럭축제</v>
       </c>
       <c r="B4" t="str">
-        <v>팝업마켓</v>
+        <v>푸드트럭</v>
       </c>
       <c r="C4" t="str">
-        <v>성수동 복합 팝업 마켓</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>인천 복합문화축제</v>
-      </c>
-      <c r="B5" t="str">
-        <v>복합문화행사</v>
-      </c>
-      <c r="C5" t="str">
-        <v>인천 송도 복합 문화 행사</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>[카테고리] 플리마켓 / 푸드트럭페스티벌 / 팝업마켓 / 복합문화행사</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>[안내] 행사명은 고유해야 합니다 (중복 불가)</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F3"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="42.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,10 +677,10 @@
         <v>행사명 *</v>
       </c>
       <c r="B1" t="str">
+        <v>장소 *</v>
+      </c>
+      <c r="C1" t="str">
         <v>주최사명 *</v>
-      </c>
-      <c r="C1" t="str">
-        <v>장소 *</v>
       </c>
       <c r="D1" t="str">
         <v>시/도 *</v>
@@ -662,106 +697,71 @@
         <v>서울밤도깨비야시장</v>
       </c>
       <c r="B2" t="str">
-        <v>서울플리마켓협회</v>
+        <v>여의도한강공원</v>
       </c>
       <c r="C2" t="str">
-        <v>서울 여의도 한강공원 멀티플라자</v>
+        <v>한강공원관리사업소</v>
       </c>
       <c r="D2" t="str">
         <v>서울</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-04-06</v>
+        <v>2026-04-12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>여의도 한강 푸드트럭</v>
+        <v>뚝섬 플리마켓</v>
       </c>
       <c r="B3" t="str">
-        <v>한강문화재단</v>
+        <v>뚝섬한강공원</v>
       </c>
       <c r="C3" t="str">
-        <v>서울 영등포구 여의도동 한강공원</v>
+        <v>서울플리마켓협회</v>
       </c>
       <c r="D3" t="str">
         <v>서울</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-18</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-04-12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>성수 팝업마켓</v>
-      </c>
-      <c r="B4" t="str">
-        <v>서울플리마켓협회</v>
-      </c>
-      <c r="C4" t="str">
-        <v>서울 성동구 성수동 2가 뚝섬로</v>
-      </c>
-      <c r="D4" t="str">
-        <v>서울</v>
-      </c>
-      <c r="E4" t="str">
         <v>2026-04-19</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2026-04-20</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>[안내] 행사명/주최사명은 위 시트와 정확히 일치해야 합니다</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>[날짜] YYYY-MM-DD 형식 (예: 2026-04-05). 당일 행사면 종료일 비워두기</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>[시/도] 서울,경기,인천,부산,대구,광주,대전,울산,세종,강원,충북,충남,전북,전남,경북,경남,제주</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="58.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>공고 제목 *</v>
+      </c>
+      <c r="B1" t="str">
+        <v>공고 내용 *</v>
+      </c>
+      <c r="C1" t="str">
         <v>행사명 *</v>
-      </c>
-      <c r="B1" t="str">
-        <v>공고 제목 *</v>
-      </c>
-      <c r="C1" t="str">
-        <v>공고 내용 *</v>
       </c>
       <c r="D1" t="str">
         <v>참가비(원)</v>
@@ -781,28 +781,28 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
+        <v>서울밤도깨비야시장 셀러 모집</v>
+      </c>
+      <c r="B2" t="str" xml:space="preserve">
+        <v xml:space="preserve">■ 모집조건
+핸드메이드 및 리빙 셀러
+■ 참가비
+부스당 50,000원</v>
+      </c>
+      <c r="C2" t="str">
         <v>서울밤도깨비야시장</v>
-      </c>
-      <c r="B2" t="str">
-        <v>[4/5~6] 서울밤도깨비야시장 셀러 모집</v>
-      </c>
-      <c r="C2" t="str" xml:space="preserve">
-        <v xml:space="preserve">서울 여의도 한강공원에서 진행되는 야시장 셀러를 모집합니다.
-모집 대상: 핸드메이드, 소품, 의류
-부스 규격: 2m x 2m
-포함: 테이블, 의자, 전기</v>
       </c>
       <c r="D2">
         <v>50000</v>
       </c>
       <c r="E2" t="str">
-        <v>카카오톡 채널 서울플리 문의</v>
+        <v>구글폼 https://forms.google.com/xxx</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-25</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-04-05</v>
       </c>
       <c r="H2" t="str">
         <v>OPEN</v>
@@ -810,51 +810,36 @@
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>여의도 한강 푸드트럭</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[4/12] 한강 푸드트럭 페스티벌 참가팀 모집</v>
-      </c>
-      <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">여의도 한강공원 푸드트럭 페스티벌 참가팀을 모집합니다.
-모집 대상: 푸드트럭 운영자
-주차: 3m x 6m
-전기: 220V 제공</v>
+        <v>뚝섬 플리마켓 셀러 모집</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">■ 모집조건
+플리마켓 판매 가능한 모든 품목
+■ 참가비
+무료</v>
+      </c>
+      <c r="C3" t="str">
+        <v>뚝섬 플리마켓</v>
       </c>
       <c r="D3">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>이메일 접수 (hangang@fest.kr)</v>
+        <v>네이버폼 링크</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-03-25</v>
+        <v>2026-04-01</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-10</v>
       </c>
       <c r="H3" t="str">
         <v>OPEN</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>[안내] 참가비: 숫자만 입력 (무료=0, 미정=비워둠)</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>[상태] OPEN (모집중) / CLOSED (마감)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>[행사명] 3_행사개최 시트의 행사명과 일치해야 합니다</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data_template.xlsx
+++ b/public/data_template.xlsx
@@ -397,22 +397,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="30.83203125" customWidth="1"/>
+    <col min="14" max="14" width="30.83203125" customWidth="1"/>
+    <col min="15" max="15" width="40.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,15 +450,24 @@
         <v>참가비(원)</v>
       </c>
       <c r="K1" t="str">
+        <v>참가비유형</v>
+      </c>
+      <c r="L1" t="str">
+        <v>푸드트럭참가비(원)</v>
+      </c>
+      <c r="M1" t="str">
+        <v>추가비용</v>
+      </c>
+      <c r="N1" t="str">
         <v>신청방법</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>공고내용</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>모집시작일</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>상태</v>
       </c>
     </row>
@@ -491,21 +503,30 @@
         <v>50000</v>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v>인스타그램 DM 신청</v>
       </c>
-      <c r="L2" t="str">
+      <c r="O2" t="str">
         <v>부스 크기 2x2m, 전기 제공</v>
       </c>
-      <c r="M2" t="str">
+      <c r="P2" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="N2" t="str">
+      <c r="Q2" t="str">
         <v>OPEN</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data_template.xlsx
+++ b/public/data_template.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="데이터입력" sheetId="1" r:id="rId1"/>
+    <sheet name="공고데이터" sheetId="1" r:id="rId1"/>
+    <sheet name="작성가이드" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -400,21 +401,21 @@
   <dimension ref="A1:Q2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="30.83203125" customWidth="1"/>
-    <col min="14" max="14" width="30.83203125" customWidth="1"/>
-    <col min="15" max="15" width="40.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
+    <col min="13" max="13" width="35.83203125" customWidth="1"/>
+    <col min="14" max="14" width="40.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
     <col min="17" max="17" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -423,102 +424,104 @@
         <v>행사명 *</v>
       </c>
       <c r="B1" t="str">
+        <v>카테고리</v>
+      </c>
+      <c r="C1" t="str">
+        <v>주최사명</v>
+      </c>
+      <c r="D1" t="str">
+        <v>장소 *</v>
+      </c>
+      <c r="E1" t="str">
+        <v>시/도</v>
+      </c>
+      <c r="F1" t="str">
+        <v>행사시작일 *</v>
+      </c>
+      <c r="G1" t="str">
+        <v>행사종료일</v>
+      </c>
+      <c r="H1" t="str">
         <v>공고제목 *</v>
       </c>
-      <c r="C1" t="str">
-        <v>모집마감일 *</v>
-      </c>
-      <c r="D1" t="str">
-        <v>주최사명</v>
-      </c>
-      <c r="E1" t="str">
-        <v>카테고리</v>
-      </c>
-      <c r="F1" t="str">
-        <v>장소</v>
-      </c>
-      <c r="G1" t="str">
-        <v>시/도</v>
-      </c>
-      <c r="H1" t="str">
-        <v>행사시작일</v>
-      </c>
       <c r="I1" t="str">
-        <v>행사종료일</v>
+        <v>공고내용</v>
       </c>
       <c r="J1" t="str">
-        <v>참가비(원)</v>
+        <v>참가비</v>
       </c>
       <c r="K1" t="str">
-        <v>참가비유형</v>
+        <v>환불규정</v>
       </c>
       <c r="L1" t="str">
-        <v>푸드트럭참가비(원)</v>
+        <v>주차지원</v>
       </c>
       <c r="M1" t="str">
-        <v>추가비용</v>
+        <v>현장지원</v>
       </c>
       <c r="N1" t="str">
         <v>신청방법</v>
       </c>
       <c r="O1" t="str">
-        <v>공고내용</v>
+        <v>모집시작일</v>
       </c>
       <c r="P1" t="str">
-        <v>모집시작일</v>
+        <v>모집마감일</v>
       </c>
       <c r="Q1" t="str">
         <v>상태</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>여의도 봄 플리마켓</v>
+        <v>홍대 플리마켓</v>
       </c>
       <c r="B2" t="str">
-        <v>2차 셀러 모집</v>
+        <v>플리마켓</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-05-01</v>
+        <v>서울플리마켓협회</v>
       </c>
       <c r="D2" t="str">
-        <v>한강마켓조합</v>
+        <v>서울 마포구 홍대 걷고싶은거리</v>
       </c>
       <c r="E2" t="str">
-        <v>플리마켓</v>
+        <v>서울</v>
       </c>
       <c r="F2" t="str">
-        <v>서울 영등포구 여의도한강공원</v>
+        <v>2026-05-10</v>
       </c>
       <c r="G2" t="str">
-        <v>서울</v>
+        <v>2026-05-11</v>
       </c>
       <c r="H2" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-05-11</v>
+        <v>2026 홍대 플리마켓 셀러 모집</v>
+      </c>
+      <c r="I2" t="str" xml:space="preserve">
+        <v xml:space="preserve">부스 크기: 2m x 2m
+전기: 220V 1구 제공
+주의사항: 천막 설치 불가</v>
       </c>
       <c r="J2" t="str">
-        <v>50000</v>
+        <v>1일 80,000원 / 2일 150,000원</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>행사 7일 전 100% 환불 / 3일 전 50% / 이후 환불 불가</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>행사장 인근 공영주차장 이용</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>현장 스텝 상주 / 테이블·의자 제공 / SNS 홍보</v>
       </c>
       <c r="N2" t="str">
-        <v>인스타그램 DM 신청</v>
+        <v>구글폼으로 신청해주세요. https://forms.gle/example</v>
       </c>
       <c r="O2" t="str">
-        <v>부스 크기 2x2m, 전기 제공</v>
+        <v>2026-04-20</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-04-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="Q2" t="str">
         <v>OPEN</v>
@@ -529,4 +532,273 @@
     <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D18"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>필드명</v>
+      </c>
+      <c r="B1" t="str">
+        <v>필수</v>
+      </c>
+      <c r="C1" t="str">
+        <v>설명</v>
+      </c>
+      <c r="D1" t="str">
+        <v>예시</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>행사명 *</v>
+      </c>
+      <c r="B2" t="str">
+        <v>필수</v>
+      </c>
+      <c r="C2" t="str">
+        <v>행사 브랜드명. 기존 행사명과 동일하면 자동 매핑됨</v>
+      </c>
+      <c r="D2" t="str">
+        <v>홍대 플리마켓</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>카테고리</v>
+      </c>
+      <c r="B3" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C3" t="str">
+        <v>플리마켓 / 푸드트럭 / 플리+푸드 전체 / 팝업스토어</v>
+      </c>
+      <c r="D3" t="str">
+        <v>플리마켓</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>주최사명</v>
+      </c>
+      <c r="B4" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C4" t="str">
+        <v>주최사 이름. 기존 주최사와 동일하면 자동 매핑됨</v>
+      </c>
+      <c r="D4" t="str">
+        <v>서울플리마켓협회</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>장소 *</v>
+      </c>
+      <c r="B5" t="str">
+        <v>필수</v>
+      </c>
+      <c r="C5" t="str">
+        <v>행사장 주소 (도로명 또는 지번)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>서울 마포구 홍대 걷고싶은거리</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>시/도</v>
+      </c>
+      <c r="B6" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C6" t="str">
+        <v>시도 구분 (자동 추출 안 될 때 직접 입력)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>서울</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>행사시작일 *</v>
+      </c>
+      <c r="B7" t="str">
+        <v>필수</v>
+      </c>
+      <c r="C7" t="str">
+        <v>YYYY-MM-DD 형식</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>행사종료일</v>
+      </c>
+      <c r="B8" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C8" t="str">
+        <v>YYYY-MM-DD 형식. 비우면 시작일과 동일</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>공고제목 *</v>
+      </c>
+      <c r="B9" t="str">
+        <v>필수</v>
+      </c>
+      <c r="C9" t="str">
+        <v>모집공고 제목</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026 홍대 플리마켓 셀러 모집</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>공고내용</v>
+      </c>
+      <c r="B10" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C10" t="str">
+        <v>부스 크기, 전기 공급, 주의사항 등 상세 내용</v>
+      </c>
+      <c r="D10" t="str">
+        <v>부스 크기: 2m x 2m</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>참가비</v>
+      </c>
+      <c r="B11" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C11" t="str">
+        <v>자유 텍스트로 입력</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1일 80,000원 / 2일 150,000원</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>환불규정</v>
+      </c>
+      <c r="B12" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C12" t="str">
+        <v>환불 가능 여부 및 조건</v>
+      </c>
+      <c r="D12" t="str">
+        <v>7일 전 100% / 3일 전 50% / 이후 불가</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>주차지원</v>
+      </c>
+      <c r="B13" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C13" t="str">
+        <v>주차 지원 여부</v>
+      </c>
+      <c r="D13" t="str">
+        <v>행사장 인근 공영주차장 이용</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>현장지원</v>
+      </c>
+      <c r="B14" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C14" t="str">
+        <v>스텝, 집기류, 홍보 등</v>
+      </c>
+      <c r="D14" t="str">
+        <v>스텝 상주 / 테이블·의자 제공</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>신청방법</v>
+      </c>
+      <c r="B15" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C15" t="str">
+        <v>신청 링크, 연락처 등</v>
+      </c>
+      <c r="D15" t="str">
+        <v>구글폼: https://forms.gle/...</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>모집시작일</v>
+      </c>
+      <c r="B16" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C16" t="str">
+        <v>YYYY-MM-DD 형식</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-04-20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>모집마감일</v>
+      </c>
+      <c r="B17" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C17" t="str">
+        <v>YYYY-MM-DD 형식</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>상태</v>
+      </c>
+      <c r="B18" t="str">
+        <v>선택</v>
+      </c>
+      <c r="C18" t="str">
+        <v>OPEN (모집중) 또는 CLOSED (마감). 기본값: OPEN</v>
+      </c>
+      <c r="D18" t="str">
+        <v>OPEN</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/data_template.xlsx
+++ b/public/data_template.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="공고데이터" sheetId="1" r:id="rId1"/>
-    <sheet name="작성가이드" sheetId="2" r:id="rId2"/>
+    <sheet name="0_안내" sheetId="1" r:id="rId1"/>
+    <sheet name="공고 데이터" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,24 +398,154 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:B23"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>FLIT 데이터 입력 양식 (V4) — 단일 시트</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>📌 작성 방법</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>"공고 데이터" 시트에 한 행에 공고 하나씩 입력하세요.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>주최사/행사/개최 정보가 같은 행에 함께 있으면 자동으로 분리되어 저장됩니다.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>같은 행사명/장소/날짜 조합은 한 번만 생성되고 공고만 추가됩니다.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>📌 필수 컬럼 (* 표시)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>·</v>
+      </c>
+      <c r="B9" t="str">
+        <v>행사명 *  — 행사 브랜드 이름</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>·</v>
+      </c>
+      <c r="B10" t="str">
+        <v>공고제목 * — 공고 헤드라인</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>📌 참가비 입력</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>·</v>
+      </c>
+      <c r="B13" t="str">
+        <v>자유 텍스트로 입력 (예: "무료", "1일 8만원", "매출의 20%", "평일 5만 / 주말 8만")</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>📌 날짜 형식</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>·</v>
+      </c>
+      <c r="B16" t="str">
+        <v>YYYY-MM-DD 권장 (예: 2026-04-10)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>·</v>
+      </c>
+      <c r="B17" t="str">
+        <v>엑셀 날짜 셀, 또는 YYYY.MM.DD, MM/DD 형식도 자동 인식</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>📌 상태 컬럼</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>·</v>
+      </c>
+      <c r="B20" t="str">
+        <v>OPEN (모집중) / CLOSED (마감)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>📌 버전</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>v4</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-04-08 — 단일 시트 통합 / 참가비 자유 텍스트 / 환불·주차·현장지원 컬럼 추가</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q4"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
-    <col min="10" max="10" width="30.83203125" customWidth="1"/>
-    <col min="11" max="11" width="35.83203125" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" customWidth="1"/>
-    <col min="13" max="13" width="35.83203125" customWidth="1"/>
-    <col min="14" max="14" width="40.83203125" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+    <col min="12" max="12" width="26.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="28.83203125" customWidth="1"/>
+    <col min="16" max="16" width="40.83203125" customWidth="1"/>
     <col min="17" max="17" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -424,381 +554,216 @@
         <v>행사명 *</v>
       </c>
       <c r="B1" t="str">
-        <v>카테고리</v>
+        <v>공고제목 *</v>
       </c>
       <c r="C1" t="str">
         <v>주최사명</v>
       </c>
       <c r="D1" t="str">
-        <v>장소 *</v>
+        <v>카테고리</v>
       </c>
       <c r="E1" t="str">
+        <v>장소</v>
+      </c>
+      <c r="F1" t="str">
         <v>시/도</v>
       </c>
-      <c r="F1" t="str">
-        <v>행사시작일 *</v>
-      </c>
       <c r="G1" t="str">
+        <v>행사시작일</v>
+      </c>
+      <c r="H1" t="str">
         <v>행사종료일</v>
       </c>
-      <c r="H1" t="str">
-        <v>공고제목 *</v>
-      </c>
       <c r="I1" t="str">
+        <v>모집시작일</v>
+      </c>
+      <c r="J1" t="str">
+        <v>모집마감일</v>
+      </c>
+      <c r="K1" t="str">
+        <v>참가비</v>
+      </c>
+      <c r="L1" t="str">
+        <v>환불규정</v>
+      </c>
+      <c r="M1" t="str">
+        <v>주차지원</v>
+      </c>
+      <c r="N1" t="str">
+        <v>현장지원</v>
+      </c>
+      <c r="O1" t="str">
+        <v>신청방법</v>
+      </c>
+      <c r="P1" t="str">
         <v>공고내용</v>
-      </c>
-      <c r="J1" t="str">
-        <v>참가비</v>
-      </c>
-      <c r="K1" t="str">
-        <v>환불규정</v>
-      </c>
-      <c r="L1" t="str">
-        <v>주차지원</v>
-      </c>
-      <c r="M1" t="str">
-        <v>현장지원</v>
-      </c>
-      <c r="N1" t="str">
-        <v>신청방법</v>
-      </c>
-      <c r="O1" t="str">
-        <v>모집시작일</v>
-      </c>
-      <c r="P1" t="str">
-        <v>모집마감일</v>
       </c>
       <c r="Q1" t="str">
         <v>상태</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>홍대 플리마켓</v>
+        <v>서울밤도깨비야시장</v>
       </c>
       <c r="B2" t="str">
-        <v>플리마켓</v>
+        <v>4월 야시장 셀러 모집</v>
       </c>
       <c r="C2" t="str">
         <v>서울플리마켓협회</v>
       </c>
       <c r="D2" t="str">
-        <v>서울 마포구 홍대 걷고싶은거리</v>
+        <v>플리마켓</v>
       </c>
       <c r="E2" t="str">
+        <v>여의도한강공원</v>
+      </c>
+      <c r="F2" t="str">
         <v>서울</v>
       </c>
-      <c r="F2" t="str">
-        <v>2026-05-10</v>
-      </c>
       <c r="G2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="H2" t="str">
-        <v>2026 홍대 플리마켓 셀러 모집</v>
-      </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">부스 크기: 2m x 2m
-전기: 220V 1구 제공
-주의사항: 천막 설치 불가</v>
+        <v>2026-04-13</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-03-25</v>
       </c>
       <c r="J2" t="str">
-        <v>1일 80,000원 / 2일 150,000원</v>
+        <v>2026-04-05</v>
       </c>
       <c r="K2" t="str">
-        <v>행사 7일 전 100% 환불 / 3일 전 50% / 이후 환불 불가</v>
+        <v>1일 8만원 / 2일 14만원</v>
       </c>
       <c r="L2" t="str">
-        <v>행사장 인근 공영주차장 이용</v>
+        <v>행사 7일 전까지 80% 환불</v>
       </c>
       <c r="M2" t="str">
-        <v>현장 스텝 상주 / 테이블·의자 제공 / SNS 홍보</v>
+        <v>인근 공영주차장 이용 (셀러 할인 없음)</v>
       </c>
       <c r="N2" t="str">
-        <v>구글폼으로 신청해주세요. https://forms.gle/example</v>
+        <v>천막·테이블 대여 가능 (유료)</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-04-20</v>
+        <v>구글폼 https://forms.google.com/xxx</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-05-05</v>
+        <v>핸드메이드/리빙 셀러 환영. 부스 2x2m 제공.</v>
       </c>
       <c r="Q2" t="str">
         <v>OPEN</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>뚝섬 플리마켓</v>
+      </c>
+      <c r="B3" t="str">
+        <v>5월 플리마켓 셀러 모집</v>
+      </c>
+      <c r="C3" t="str">
+        <v>서울플리마켓협회</v>
+      </c>
+      <c r="D3" t="str">
+        <v>플리+푸드</v>
+      </c>
+      <c r="E3" t="str">
+        <v>뚝섬한강공원</v>
+      </c>
+      <c r="F3" t="str">
+        <v>서울</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="K3" t="str">
+        <v>무료</v>
+      </c>
+      <c r="L3" t="str">
+        <v>환불 없음</v>
+      </c>
+      <c r="M3" t="str">
+        <v>주차 가능 (무료)</v>
+      </c>
+      <c r="N3" t="str">
+        <v>전기·테이블 미제공</v>
+      </c>
+      <c r="O3" t="str">
+        <v>인스타 DM @flit_market</v>
+      </c>
+      <c r="P3" t="str">
+        <v>플리마켓 판매 가능한 모든 품목 환영.</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>OPEN</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>한강 푸드트럭 페스티벌</v>
+      </c>
+      <c r="B4" t="str">
+        <v>4월 푸드트럭 모집</v>
+      </c>
+      <c r="C4" t="str">
+        <v>한강사업본부</v>
+      </c>
+      <c r="D4" t="str">
+        <v>푸드트럭</v>
+      </c>
+      <c r="E4" t="str">
+        <v>반포한강공원</v>
+      </c>
+      <c r="F4" t="str">
+        <v>서울</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="K4" t="str">
+        <v>3일 30만원 (전기/수도 포함)</v>
+      </c>
+      <c r="L4" t="str">
+        <v>행사 14일 전까지 100% 환불</v>
+      </c>
+      <c r="M4" t="str">
+        <v>셀러 전용 주차 1대 제공</v>
+      </c>
+      <c r="N4" t="str">
+        <v>전기 220V, 수도 공급</v>
+      </c>
+      <c r="O4" t="str">
+        <v>카카오톡 채널 @hangang-food</v>
+      </c>
+      <c r="P4" t="str">
+        <v>푸드트럭 운영자 모집. HACCP 인증 우대.</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>OPEN</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="45.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>필드명</v>
-      </c>
-      <c r="B1" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C1" t="str">
-        <v>설명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>예시</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>행사명 *</v>
-      </c>
-      <c r="B2" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C2" t="str">
-        <v>행사 브랜드명. 기존 행사명과 동일하면 자동 매핑됨</v>
-      </c>
-      <c r="D2" t="str">
-        <v>홍대 플리마켓</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>카테고리</v>
-      </c>
-      <c r="B3" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C3" t="str">
-        <v>플리마켓 / 푸드트럭 / 플리+푸드 전체 / 팝업스토어</v>
-      </c>
-      <c r="D3" t="str">
-        <v>플리마켓</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>주최사명</v>
-      </c>
-      <c r="B4" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C4" t="str">
-        <v>주최사 이름. 기존 주최사와 동일하면 자동 매핑됨</v>
-      </c>
-      <c r="D4" t="str">
-        <v>서울플리마켓협회</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>장소 *</v>
-      </c>
-      <c r="B5" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C5" t="str">
-        <v>행사장 주소 (도로명 또는 지번)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>서울 마포구 홍대 걷고싶은거리</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>시/도</v>
-      </c>
-      <c r="B6" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C6" t="str">
-        <v>시도 구분 (자동 추출 안 될 때 직접 입력)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>서울</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>행사시작일 *</v>
-      </c>
-      <c r="B7" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C7" t="str">
-        <v>YYYY-MM-DD 형식</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>행사종료일</v>
-      </c>
-      <c r="B8" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C8" t="str">
-        <v>YYYY-MM-DD 형식. 비우면 시작일과 동일</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-11</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>공고제목 *</v>
-      </c>
-      <c r="B9" t="str">
-        <v>필수</v>
-      </c>
-      <c r="C9" t="str">
-        <v>모집공고 제목</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026 홍대 플리마켓 셀러 모집</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>공고내용</v>
-      </c>
-      <c r="B10" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C10" t="str">
-        <v>부스 크기, 전기 공급, 주의사항 등 상세 내용</v>
-      </c>
-      <c r="D10" t="str">
-        <v>부스 크기: 2m x 2m</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>참가비</v>
-      </c>
-      <c r="B11" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C11" t="str">
-        <v>자유 텍스트로 입력</v>
-      </c>
-      <c r="D11" t="str">
-        <v>1일 80,000원 / 2일 150,000원</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>환불규정</v>
-      </c>
-      <c r="B12" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C12" t="str">
-        <v>환불 가능 여부 및 조건</v>
-      </c>
-      <c r="D12" t="str">
-        <v>7일 전 100% / 3일 전 50% / 이후 불가</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>주차지원</v>
-      </c>
-      <c r="B13" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C13" t="str">
-        <v>주차 지원 여부</v>
-      </c>
-      <c r="D13" t="str">
-        <v>행사장 인근 공영주차장 이용</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>현장지원</v>
-      </c>
-      <c r="B14" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C14" t="str">
-        <v>스텝, 집기류, 홍보 등</v>
-      </c>
-      <c r="D14" t="str">
-        <v>스텝 상주 / 테이블·의자 제공</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>신청방법</v>
-      </c>
-      <c r="B15" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C15" t="str">
-        <v>신청 링크, 연락처 등</v>
-      </c>
-      <c r="D15" t="str">
-        <v>구글폼: https://forms.gle/...</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>모집시작일</v>
-      </c>
-      <c r="B16" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C16" t="str">
-        <v>YYYY-MM-DD 형식</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-04-20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>모집마감일</v>
-      </c>
-      <c r="B17" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C17" t="str">
-        <v>YYYY-MM-DD 형식</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-05-05</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>상태</v>
-      </c>
-      <c r="B18" t="str">
-        <v>선택</v>
-      </c>
-      <c r="C18" t="str">
-        <v>OPEN (모집중) 또는 CLOSED (마감). 기본값: OPEN</v>
-      </c>
-      <c r="D18" t="str">
-        <v>OPEN</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data_template.xlsx
+++ b/public/data_template.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="0_안내" sheetId="1" r:id="rId1"/>
-    <sheet name="공고 데이터" sheetId="2" r:id="rId2"/>
+    <sheet name="공고 데이터" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,155 +397,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>FLIT 데이터 입력 양식 (V4) — 단일 시트</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>📌 작성 방법</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>1</v>
-      </c>
-      <c r="B4" t="str">
-        <v>"공고 데이터" 시트에 한 행에 공고 하나씩 입력하세요.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2</v>
-      </c>
-      <c r="B5" t="str">
-        <v>주최사/행사/개최 정보가 같은 행에 함께 있으면 자동으로 분리되어 저장됩니다.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3</v>
-      </c>
-      <c r="B6" t="str">
-        <v>같은 행사명/장소/날짜 조합은 한 번만 생성되고 공고만 추가됩니다.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>📌 필수 컬럼 (* 표시)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>·</v>
-      </c>
-      <c r="B9" t="str">
-        <v>행사명 *  — 행사 브랜드 이름</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>·</v>
-      </c>
-      <c r="B10" t="str">
-        <v>공고제목 * — 공고 헤드라인</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>📌 참가비 입력</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>·</v>
-      </c>
-      <c r="B13" t="str">
-        <v>자유 텍스트로 입력 (예: "무료", "1일 8만원", "매출의 20%", "평일 5만 / 주말 8만")</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>📌 날짜 형식</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>·</v>
-      </c>
-      <c r="B16" t="str">
-        <v>YYYY-MM-DD 권장 (예: 2026-04-10)</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>·</v>
-      </c>
-      <c r="B17" t="str">
-        <v>엑셀 날짜 셀, 또는 YYYY.MM.DD, MM/DD 형식도 자동 인식</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>📌 상태 컬럼</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>·</v>
-      </c>
-      <c r="B20" t="str">
-        <v>OPEN (모집중) / CLOSED (마감)</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>📌 버전</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>v4</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2026-04-08 — 단일 시트 통합 / 참가비 자유 텍스트 / 환불·주차·현장지원 컬럼 추가</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:T2"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="28.83203125" customWidth="1"/>
-    <col min="16" max="16" width="40.83203125" customWidth="1"/>
-    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="45.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="14" max="14" width="25.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" customWidth="1"/>
+    <col min="20" max="20" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,45 +432,54 @@
         <v>주최사명</v>
       </c>
       <c r="D1" t="str">
+        <v>주최사 연락처</v>
+      </c>
+      <c r="E1" t="str">
+        <v>주최사 인스타그램</v>
+      </c>
+      <c r="F1" t="str">
         <v>카테고리</v>
       </c>
-      <c r="E1" t="str">
-        <v>장소</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>장소 *</v>
+      </c>
+      <c r="H1" t="str">
         <v>시/도</v>
       </c>
-      <c r="G1" t="str">
-        <v>행사시작일</v>
-      </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>행사시작일 *</v>
+      </c>
+      <c r="J1" t="str">
         <v>행사종료일</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
+        <v>공고내용</v>
+      </c>
+      <c r="L1" t="str">
+        <v>참가비</v>
+      </c>
+      <c r="M1" t="str">
+        <v>신청방법</v>
+      </c>
+      <c r="N1" t="str">
+        <v>환불규정</v>
+      </c>
+      <c r="O1" t="str">
+        <v>주차지원</v>
+      </c>
+      <c r="P1" t="str">
+        <v>현장지원</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>모집대상</v>
+      </c>
+      <c r="R1" t="str">
         <v>모집시작일</v>
       </c>
-      <c r="J1" t="str">
-        <v>모집마감일</v>
-      </c>
-      <c r="K1" t="str">
-        <v>참가비</v>
-      </c>
-      <c r="L1" t="str">
-        <v>환불규정</v>
-      </c>
-      <c r="M1" t="str">
-        <v>주차지원</v>
-      </c>
-      <c r="N1" t="str">
-        <v>현장지원</v>
-      </c>
-      <c r="O1" t="str">
-        <v>신청방법</v>
-      </c>
-      <c r="P1" t="str">
-        <v>공고내용</v>
-      </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
+        <v>모집마감일 *</v>
+      </c>
+      <c r="T1" t="str">
         <v>상태</v>
       </c>
     </row>
@@ -607,163 +488,66 @@
         <v>서울밤도깨비야시장</v>
       </c>
       <c r="B2" t="str">
-        <v>4월 야시장 셀러 모집</v>
+        <v>2026년 서울밤도깨비 셀러 모집</v>
       </c>
       <c r="C2" t="str">
-        <v>서울플리마켓협회</v>
+        <v>서울특별시</v>
       </c>
       <c r="D2" t="str">
+        <v>010-1234-5678</v>
+      </c>
+      <c r="E2" t="str">
+        <v>@seoul_night</v>
+      </c>
+      <c r="F2" t="str">
         <v>플리마켓</v>
       </c>
-      <c r="E2" t="str">
-        <v>여의도한강공원</v>
-      </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>여의도 한강공원</v>
+      </c>
+      <c r="H2" t="str">
         <v>서울</v>
       </c>
-      <c r="G2" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-04-13</v>
-      </c>
       <c r="I2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-05-01</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-05-03</v>
       </c>
       <c r="K2" t="str">
-        <v>1일 8만원 / 2일 14만원</v>
+        <v>여의도 한강공원에서 진행되는 야간 플리마켓입니다.</v>
       </c>
       <c r="L2" t="str">
-        <v>행사 7일 전까지 80% 환불</v>
+        <v>1일 80,000원</v>
       </c>
       <c r="M2" t="str">
-        <v>인근 공영주차장 이용 (셀러 할인 없음)</v>
+        <v>온라인 신청 (구글폼)</v>
       </c>
       <c r="N2" t="str">
-        <v>천막·테이블 대여 가능 (유료)</v>
+        <v>행사 7일 전까지 전액 환불</v>
       </c>
       <c r="O2" t="str">
-        <v>구글폼 https://forms.google.com/xxx</v>
+        <v>주차 가능 (유료)</v>
       </c>
       <c r="P2" t="str">
-        <v>핸드메이드/리빙 셀러 환영. 부스 2x2m 제공.</v>
+        <v>텐트, 테이블 제공</v>
       </c>
       <c r="Q2" t="str">
-        <v>OPEN</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>뚝섬 플리마켓</v>
-      </c>
-      <c r="B3" t="str">
-        <v>5월 플리마켓 셀러 모집</v>
-      </c>
-      <c r="C3" t="str">
-        <v>서울플리마켓협회</v>
-      </c>
-      <c r="D3" t="str">
-        <v>플리+푸드</v>
-      </c>
-      <c r="E3" t="str">
-        <v>뚝섬한강공원</v>
-      </c>
-      <c r="F3" t="str">
-        <v>서울</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="K3" t="str">
-        <v>무료</v>
-      </c>
-      <c r="L3" t="str">
-        <v>환불 없음</v>
-      </c>
-      <c r="M3" t="str">
-        <v>주차 가능 (무료)</v>
-      </c>
-      <c r="N3" t="str">
-        <v>전기·테이블 미제공</v>
-      </c>
-      <c r="O3" t="str">
-        <v>인스타 DM @flit_market</v>
-      </c>
-      <c r="P3" t="str">
-        <v>플리마켓 판매 가능한 모든 품목 환영.</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>OPEN</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>한강 푸드트럭 페스티벌</v>
-      </c>
-      <c r="B4" t="str">
-        <v>4월 푸드트럭 모집</v>
-      </c>
-      <c r="C4" t="str">
-        <v>한강사업본부</v>
-      </c>
-      <c r="D4" t="str">
-        <v>푸드트럭</v>
-      </c>
-      <c r="E4" t="str">
-        <v>반포한강공원</v>
-      </c>
-      <c r="F4" t="str">
-        <v>서울</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-04-25</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="I4" t="str">
+        <v>seller</v>
+      </c>
+      <c r="R2" t="str">
         <v>2026-04-01</v>
       </c>
-      <c r="J4" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="K4" t="str">
-        <v>3일 30만원 (전기/수도 포함)</v>
-      </c>
-      <c r="L4" t="str">
-        <v>행사 14일 전까지 100% 환불</v>
-      </c>
-      <c r="M4" t="str">
-        <v>셀러 전용 주차 1대 제공</v>
-      </c>
-      <c r="N4" t="str">
-        <v>전기 220V, 수도 공급</v>
-      </c>
-      <c r="O4" t="str">
-        <v>카카오톡 채널 @hangang-food</v>
-      </c>
-      <c r="P4" t="str">
-        <v>푸드트럭 운영자 모집. HACCP 인증 우대.</v>
-      </c>
-      <c r="Q4" t="str">
+      <c r="S2" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="T2" t="str">
         <v>OPEN</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T2"/>
   </ignoredErrors>
 </worksheet>
 </file>